--- a/AAII_Financials/Yearly/RCKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RCKY_YR_FIN.xlsx
@@ -3029,7 +3029,7 @@
         <v>11200</v>
       </c>
       <c r="F59" s="3">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="G59" s="3">
         <v>1200</v>
